--- a/停電作業計画書_第4回_受電所/停電作業計画書_第4回_受電所.xlsx
+++ b/停電作業計画書_第4回_受電所/停電作業計画書_第4回_受電所.xlsx
@@ -25,17 +25,17 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'表紙'!$A$1:$H$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'目次'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'1.概要 2.工程管理'!$A$1:$J$88</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'1.概要 2.工程管理'!$A$1:$J$89</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3.現場組織表'!$A$1:$F$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'4.緊急連絡表'!$A$1:$D$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.安全対策'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5.安全対策'!$A$1:$D$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'6.作業方法'!$A$1:$G$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'7.タイムスケジュール'!$A$1:$I$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'7.タイムスケジュール'!$A$1:$I$105</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'8.配置図'!$A$1:$F$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'9.品質管理'!$A$1:$G$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'10.チェックリスト'!$A$1:$F$101</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'11.測定記録'!$A$1:$J$148</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'12.作業員名簿'!$A$1:$H$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'12.作業員名簿'!$A$1:$H$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'※要確認事項'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -925,7 +925,7 @@
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>令和8年12月23日（水）・24日（木）・25日（金）　各日9:00～16:00
-（12/25は15:00頃からの試験・検査終了後に復電し、17:45頃終了予定。
+（12/25は15:00頃からの試験・検査終了後に復電し、17:00頃終了予定。
 高圧は12/23 9:00から12/25の復電まで連続停電）</t>
         </is>
       </c>
@@ -3860,7 +3860,7 @@
       <c r="E75" s="22" t="n"/>
       <c r="F75" s="22" t="n"/>
     </row>
-    <row r="76" ht="29.9" customHeight="1">
+    <row r="76" ht="45.5" customHeight="1">
       <c r="A76" s="22" t="inlineStr">
         <is>
           <t>5</t>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B76" s="23" t="inlineStr">
         <is>
-          <t>関西電気保安協会による試験・検査が終了し、結果が良好であることを確認したか</t>
+          <t>受電所の発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続を、高圧停電・作業用接地中に完了したか</t>
         </is>
       </c>
       <c r="C76" s="22" t="n"/>
@@ -3876,7 +3876,7 @@
       <c r="E76" s="22" t="n"/>
       <c r="F76" s="22" t="n"/>
     </row>
-    <row r="77" ht="26" customHeight="1">
+    <row r="77" ht="29.9" customHeight="1">
       <c r="A77" s="22" t="inlineStr">
         <is>
           <t>6</t>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>新設A/B母線へ作業用接地を再取付し、記録したか</t>
+          <t>関西電気保安協会による試験・検査が終了し、結果が良好であることを確認したか</t>
         </is>
       </c>
       <c r="C77" s="22" t="n"/>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>試験のため一時取り外した作業用接地を再取付し、記録したか</t>
+          <t>新設A/B母線へ作業用接地を再取付し、記録したか</t>
         </is>
       </c>
       <c r="C78" s="22" t="n"/>
@@ -3908,7 +3908,7 @@
       <c r="E78" s="22" t="n"/>
       <c r="F78" s="22" t="n"/>
     </row>
-    <row r="79" ht="45.5" customHeight="1">
+    <row r="79" ht="26" customHeight="1">
       <c r="A79" s="22" t="inlineStr">
         <is>
           <t>8</t>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>受電所の発電機停止・仮設ケーブル切離し・低圧母線絶縁抵抗測定・2次導体母線側接続を、高圧停電・作業用接地中に完了したか</t>
+          <t>試験のため一時取り外した作業用接地を再取付し、記録したか</t>
         </is>
       </c>
       <c r="C79" s="22" t="n"/>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>復電前の絶縁抵抗測定（2次導体接続部を含む）を行い、規定値以上であることを確認したか</t>
+          <t>復電前の絶縁抵抗測定（保安協会の試験時、2次導体接続部を含む）の結果が規定値以上であることを確認したか</t>
         </is>
       </c>
       <c r="C81" s="22" t="n"/>
@@ -7253,7 +7253,7 @@
     <row r="147" ht="28.6" customHeight="1">
       <c r="A147" s="33" t="inlineStr">
         <is>
-          <t>12/25 運転停止時（15:40～16:15頃）</t>
+          <t>12/25 運転停止時（14:15～15:35頃）</t>
         </is>
       </c>
       <c r="B147" s="32" t="n"/>
@@ -7530,7 +7530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.1" customWidth="1" min="1" max="1"/>
@@ -8946,29 +8946,25 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="44.6" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>消防・環境</t>
-        </is>
-      </c>
+    <row r="57" ht="29.4" customHeight="1">
+      <c r="A57" s="25" t="n"/>
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>ABC粉末消火器</t>
+          <t>試験用・照明用小型発電機</t>
         </is>
       </c>
       <c r="D57" s="10" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="26" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>要確認（保安協会の試験器・照明用）</t>
         </is>
       </c>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="26" t="inlineStr">
         <is>
-          <t>発電機各台に1本以上</t>
+          <t>1台/始業前点検</t>
         </is>
       </c>
     </row>
@@ -8977,32 +8973,82 @@
       <c r="B58" s="8" t="n"/>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>オイルパン・吸着マット</t>
+          <t>投光器（バッテリー式等）</t>
         </is>
       </c>
       <c r="D58" s="10" t="n"/>
       <c r="E58" s="8" t="n"/>
       <c r="F58" s="26" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>電気室・引込柱の照明用</t>
         </is>
       </c>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="26" t="inlineStr">
         <is>
+          <t>必要数</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44.6" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>消防・環境</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>ABC粉末消火器</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>発電機各台に1本以上</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="25" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>オイルパン・吸着マット</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="26" t="inlineStr">
+        <is>
           <t>一式</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="73">
     <mergeCell ref="C54:E54"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="C50:E50"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="C55:E55"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A49:B49"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="C40:E40"/>
@@ -9010,10 +9056,13 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C59:E59"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="C51:E51"/>
     <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="C60:E60"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="F53:G53"/>
@@ -9055,6 +9104,7 @@
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F60:G60"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
@@ -9523,7 +9573,7 @@
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>12/23の仮設切替（～11:45頃）、12/25の商用復旧（15:40～17:30頃）は、停電作業員4名で3か所を順に作業する前提の予定時刻である。切替作業、復電操作（接地9組の取外し～饋電VCB投入）及び引込柱・各棟間の移動の所要時間を確認し、必要に応じ人員配置を見直す。</t>
+          <t>12/23の仮設切替（～11:45頃）、12/25の商用復旧（14:15～16:45頃）は、停電作業員4名で3か所を順に作業する前提の予定時刻である。切替作業、復電操作（接地9組の取外し～饋電VCB投入）及び引込柱・各棟間の移動の所要時間を確認し、必要に応じ人員配置を見直す。</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
@@ -9554,7 +9604,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="44.6" customHeight="1">
+    <row r="24" ht="68" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
           <t>19</t>
@@ -9562,17 +9612,17 @@
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>試験・検査の所要時間</t>
+          <t>試験・検査の所要時間・電源</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>保安協会の試験・検査を15:00～16:00（1時間）で計画した。試験項目（絶縁耐力・継電器試験・受電前検査）・所要時間・試験範囲（2次導体母線側接続部の扱い）を保安協会と協議する。</t>
+          <t>保安協会の試験・検査を15:00～16:00（1時間）で計画した。2次導体接続部を含めて試験することを確認し、試験項目（絶縁耐力・継電器試験・受電前検査）・所要時間を保安協会と協議する。受電所は14:15以降無電源となるため、試験器の電源（試験用小型発電機等）を確認する。</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>7・11</t>
+          <t>7・11・12.1</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9670,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56.3" customHeight="1">
+    <row r="27" ht="79.7" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
           <t>22</t>
@@ -9633,7 +9683,7 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>打合せでは17:00頃終了としていたが、試験・検査（15:00～16:00）後の復電操作に安全上必要な時間を見込むと17:45頃の終了となる。部隊・監督官の了承を得るか、試験時間の短縮等で17:00頃に収める方法を協議する。</t>
+          <t>17:00頃終了とするため、受電所の発電機切離し・2次導体接続を試験・検査の前（14:15頃～）に、整備格納庫・補給倉庫棟の切離しを試験・検査と並行して行う工程とした。このため受電所の低圧負荷（管制負荷を含む可能性あり）は14:15頃～16:45頃停電となる。部隊の了承を得るとともに、試験・検査を15:00～16:00で終える必要があるため保安協会と時間を協議する。</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
@@ -9968,7 +10018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.1" customWidth="1" min="1" max="1"/>
@@ -11272,7 +11322,7 @@
       </c>
       <c r="J70" s="8" t="n"/>
     </row>
-    <row r="71" ht="79.7" customHeight="1">
+    <row r="71" ht="91.40000000000001" customHeight="1">
       <c r="A71" s="25" t="inlineStr">
         <is>
           <t>12月25日
@@ -11288,7 +11338,7 @@
       </c>
       <c r="D71" s="26" t="inlineStr">
         <is>
-          <t>結線、自主試験、関西電気保安協会による試験・検査（15:00頃～）、発電機停止・仮設切離し（3か所）、作業用接地取外し、PAS投入・受電、各VCB・LBS投入、各棟へ送電・負荷復旧（当日復電）</t>
+          <t>結線、自主試験、受電所の発電機停止・2次導体接続（14:15頃～）、関西電気保安協会による試験・検査（15:00頃～、並行して整備格納庫・補給倉庫棟の発電機停止・仮設切離し）、作業用接地取外し、PAS投入・受電、各VCB・LBS投入、各棟へ送電・負荷復旧（当日復電）</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
@@ -11299,7 +11349,7 @@
           <t>9:00～
 試験・検査
 後に復電
-17:45頃
+17:00頃
 終了予定</t>
         </is>
       </c>
@@ -11374,7 +11424,7 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>②　作業時期　:　停電作業は令和8年12月23日（水）・24日（木）・25日（金）の9:00～16:00（作業前ミーティングは8:30～）とする。12/25は15:00頃からの試験・検査終了後に復電し、商用への切替・負荷確認を含め17:45頃の終了を予定する。引込柱PASの開放により、高圧は12/23 9:00から12/25の復電まで連続して停電し、夜間は仮設発電機にて受電所・整備格納庫・補給倉庫棟の低圧負荷へ給電を継続する。</t>
+          <t>②　作業時期　:　停電作業は令和8年12月23日（水）・24日（木）・25日（金）の9:00～16:00（作業前ミーティングは8:30～）とする。12/25は15:00頃からの試験・検査終了後に復電し、商用への切替・負荷確認を含め17:00頃の終了を予定する。引込柱PASの開放により、高圧は12/23 9:00から12/25の復電まで連続して停電し、夜間は仮設発電機にて受電所・整備格納庫・補給倉庫棟の低圧負荷へ給電を継続する。</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11440,7 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>④　停電の承諾　:　施設全体の停電（約57時間（12/23 9:00頃～12/25 17:30頃））、仮設発電機への切替時（12/23 9:00～11:45頃）及び商用への復旧時（12/25 15:40～17:30頃）に生じる停電、並びに仮設給電を行わない建物・負荷の停止について、事前に部隊及び監督官の承諾を得る。部隊との検討・調整事項は「6.4」による。</t>
+          <t>④　停電の承諾　:　施設全体の停電（約56時間（12/23 9:00頃～12/25 16:45頃））、仮設発電機への切替時（12/23 9:00～11:45頃）及び商用への復旧時（12/25 14:15～16:45頃）に生じる停電、並びに仮設給電を行わない建物・負荷の停止について、事前に部隊及び監督官の承諾を得る。部隊との検討・調整事項は「6.4」による。</t>
         </is>
       </c>
     </row>
@@ -11410,18 +11460,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="20.6" customHeight="1">
-      <c r="A82" s="18" t="inlineStr">
+    <row r="82" ht="6" customHeight="1">
+      <c r="A82" s="1" t="n"/>
+    </row>
+    <row r="83" ht="20.6" customHeight="1">
+      <c r="A83" s="18" t="inlineStr">
         <is>
           <t>2.3　仮設計画（ED-02　仮設工事　による）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="60.3" customHeight="1">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>①　受電所：受電所外部に仮設発電機400kVA×3台を設置し、CET150sq（FEP100）×9条にて⑥変圧器盤1・⑦変圧器盤2・⑧変圧器盤3・⑨変圧器盤4・⑭変圧器盤5の低圧側へ接続する。号機と接続盤の対応、接続点及び発電機の出力電圧（⑥は単相3線×2回路、⑭は440-254V）は要確認事項とし、確定後に記入する。</t>
         </is>
       </c>
     </row>
@@ -11429,44 +11474,52 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>②　整備格納庫：第3回と同様に仮設発電機400kVA×3台を設置し、CET150sq（FEP100）×9条にて1号機→No.1低圧動力盤②・No.2低圧動力盤③（計3条）、2号機→No.1低圧電灯盤④（3条・単相3線）、3号機→No.2低圧電灯盤⑤（3条・単相3線）へ接続する。非常動力盤⑥は仮設給電の対象外とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="31.3" customHeight="1">
+          <t>①　受電所：受電所外部に仮設発電機400kVA×3台を設置し、CET150sq（FEP100）×9条にて⑥変圧器盤1・⑦変圧器盤2・⑧変圧器盤3・⑨変圧器盤4・⑭変圧器盤5の低圧側へ接続する。号機と接続盤の対応、接続点及び発電機の出力電圧（⑥は単相3線×2回路、⑭は440-254V）は要確認事項とし、確定後に記入する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60.3" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>③　補給倉庫棟：仮設発電機400kVA×2台を設置し、CET150sq（FEP100）×6条にて②③④盤へ接続する。号機と接続盤の対応は要確認事項とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="60.3" customHeight="1">
+          <t>②　整備格納庫：第3回と同様に仮設発電機400kVA×3台を設置し、CET150sq（FEP100）×9条にて1号機→No.1低圧動力盤②・No.2低圧動力盤③（計3条）、2号機→No.1低圧電灯盤④（3条・単相3線）、3号機→No.2低圧電灯盤⑤（3条・単相3線）へ接続する。非常動力盤⑥は仮設給電の対象外とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="31.3" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>④　整備格納庫・補給倉庫棟は高圧機器の改修を行わないため、仮設発電機から変圧器を介した高圧側への逆送を防止する措置をとる。措置の方法は電気主任技術者・別川製作所と確認のうえ決定する（要確認事項）。いずれの盤も1盤に複数台の発電機が接続されないようにする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="110.9" customHeight="1">
+          <t>③　補給倉庫棟：仮設発電機400kVA×2台を設置し、CET150sq（FEP100）×6条にて②③④盤へ接続する。号機と接続盤の対応は要確認事項とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60.3" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>⑤　運転時間は12/23 10:35～11:45頃（設置場所ごとに給電開始）～12/25 15:40～16:15頃（設置場所ごとに停止）の夜間連続運転（2夜）とし、燃料は軽油40,550.4L（24時間×3日×8台×70.4L/h）を見込む（受電所・整備格納庫 各15,206.4L、補給倉庫棟10,137.6L）。受電所・整備格納庫では3台で約211L/hを消費し夜間の補給が必要となるため、発電機の燃料タンク容量、補給方法（夜間の給油を含む）及び現場の貯蔵量を確認のうえ決定する（要確認事項）。軽油の貯蔵・取扱いが指定数量の1/5（200L）以上となる場合は火災予防条例による少量危険物の届出を、指定数量（1,000L）以上となる場合は所轄消防署の仮貯蔵・仮取扱いの承認を受ける（発電機タンク内の燃料を含めて算定）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18.6" customHeight="1">
+          <t>④　整備格納庫・補給倉庫棟は高圧機器の改修を行わないため、仮設発電機から変圧器を介した高圧側への逆送を防止する措置をとる。措置の方法は電気主任技術者・別川製作所と確認のうえ決定する（要確認事項）。いずれの盤も1盤に複数台の発電機が接続されないようにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="110.9" customHeight="1">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
+          <t>⑤　運転時間は12/23 10:35～11:45頃（設置場所ごとに給電開始）～12/25 14:15～15:35頃（設置場所ごとに停止）の夜間連続運転（2夜）とし、燃料は軽油40,550.4L（24時間×3日×8台×70.4L/h）を見込む（受電所・整備格納庫 各15,206.4L、補給倉庫棟10,137.6L）。受電所・整備格納庫では3台で約211L/hを消費し夜間の補給が必要となるため、発電機の燃料タンク容量、補給方法（夜間の給油を含む）及び現場の貯蔵量を確認のうえ決定する（要確認事項）。軽油の貯蔵・取扱いが指定数量の1/5（200L）以上となる場合は火災予防条例による少量危険物の届出を、指定数量（1,000L）以上となる場合は所轄消防署の仮貯蔵・仮取扱いの承認を受ける（発電機タンク内の燃料を含めて算定）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18.6" customHeight="1">
+      <c r="A89" s="1" t="n"/>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
           <t>⑥　詳細は「8.1　仮設設備の設置内容」による。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="170">
+  <mergeCells count="171">
     <mergeCell ref="F54:J54"/>
     <mergeCell ref="F63:J63"/>
     <mergeCell ref="D68:G68"/>
@@ -11487,6 +11540,7 @@
     <mergeCell ref="D35:J35"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C50:D50"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="I71:J71"/>
     <mergeCell ref="A56:B56"/>
@@ -11538,6 +11592,7 @@
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="B80:J80"/>
+    <mergeCell ref="B89:J89"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="B79:J79"/>
@@ -11566,7 +11621,6 @@
     <mergeCell ref="F55:J55"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="C44:D44"/>
-    <mergeCell ref="B83:J83"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A55:B55"/>
@@ -11653,7 +11707,7 @@
     <brk id="23" min="0" max="16383" man="1"/>
     <brk id="52" min="0" max="16383" man="1"/>
     <brk id="64" min="0" max="16383" man="1"/>
-    <brk id="81" min="0" max="16383" man="1"/>
+    <brk id="80" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -13127,7 +13181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.1" customWidth="1" min="1" max="1"/>
@@ -13702,63 +13756,83 @@
     <row r="49" ht="44.6" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>日没後の引込柱でのPAS操作</t>
+          <t>受電所が無電源となる間
+（12/25 14:15～16:40頃）</t>
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>12/25のPAS投入は日没後となるため、投光器で引込柱周辺・足元を照明し、操作位置・退避位置を事前に確認する。PAS操作補助員が照明・監視を行う。</t>
+          <t>電気室は投光器（バッテリー式等）で照明し、足元・操作位置を確保する。保安協会の試験器等の電源は試験用小型発電機等を準備する（要確認）。</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>足立</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="44.6" customHeight="1">
+          <t>中村</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="56.3" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>悪天候（強風・大雪・雷）</t>
+          <t>薄暮時の引込柱でのPAS操作</t>
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="26" t="inlineStr">
         <is>
+          <t>12/25のPAS投入（16:20頃）は日没前後の薄暮時となり、作業が遅れた場合は日没後となるため、投光器で引込柱周辺・足元を照明し、操作位置・退避位置を事前に確認する。PAS操作補助員が照明・監視を行う。</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="44.6" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>悪天候（強風・大雪・雷）</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
           <t>10分間平均風速10m/s以上、降雪25cm以上、雷光・雷鳴の間隔が短い場合は作業を中止する。特に揚重作業は風速10m/s以上で中止する。</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="6" customHeight="1">
-      <c r="A51" s="1" t="n"/>
-    </row>
-    <row r="52" ht="20.6" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="52" ht="6" customHeight="1">
+      <c r="A52" s="1" t="n"/>
+    </row>
+    <row r="53" ht="20.6" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>5.5　保護具・安全器具</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="73" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="inlineStr">
+    <row r="54" ht="73" customHeight="1">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>高圧絶縁用保護具（ヘルメット・絶縁手袋・絶縁長靴）、絶縁用防具、高圧検電器、放電棒、短絡接地器具、操作禁止札・施錠具（PAS・受電所・各棟用）、絶縁シート、墜落制止用器具、保護めがね、防寒具、カラーコーン・バリケード、消火器、投光器（冬季は日没が早いため必ず携行）、玉掛け用具（ナイロンスリング・シャックル）、無線機</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="54">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -13768,8 +13842,8 @@
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="B53:D53"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A28:D28"/>
@@ -13777,7 +13851,6 @@
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A51:D51"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:D24"/>
@@ -13793,6 +13866,7 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A38:B38"/>
@@ -14008,7 +14082,7 @@
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>①作業前ミーティング・KY　→　②新設機器結線・饋電/引込ケーブル端末接続（接地は1回線ずつ付替え）〔別川〕　→　③変圧器一次結線・新設2次導体の変圧器側結線（母線側未接続）・タップ設定・温度計配線、コンデンサ結線〔別川・アート〕、撤去品の積込・搬出〔AR〕　→　④A/B母線の接地再取付、接地線接続・自主試験　→　⑤関西電気保安協会による試験・検査（15:00頃～）　→　⑥3か所の発電機停止・仮設切離し、受電所の2次導体母線側接続・復電前絶縁抵抗測定　→　⑦受電所作業者集合・別棟完了報告受領・作業用接地取外し・3PDS投入（無電圧）→ PAS投入【高圧受電】→ 受電VCB・母線連絡VCB・LBS投入 → 饋電VCB投入【商用復旧】　→　⑧各棟の負荷復旧・VWC投入・機能確認（部隊立会）・完了報告</t>
+          <t>①作業前ミーティング・KY　→　②新設機器結線・饋電/引込ケーブル端末接続（接地は1回線ずつ付替え）〔別川〕　→　③変圧器一次結線・新設2次導体の変圧器側結線（母線側未接続）・タップ設定・温度計配線、コンデンサ結線〔別川・アート〕、撤去品の積込・搬出〔AR〕　→　④A/B母線の接地再取付、接地線接続・自主試験　→　⑤受電所の発電機停止・仮設切離し・2次導体母線側接続（14:15頃～）　→　⑥関西電気保安協会による試験・検査（15:00頃～、2次導体接続部を含む）、並行して整備格納庫・補給倉庫棟の発電機停止・仮設切離し　→　⑦受電所作業者集合・別棟完了報告受領・作業用接地取外し・3PDS投入（無電圧）→ PAS投入【高圧受電】→ 受電VCB・母線連絡VCB・LBS投入 → 饋電VCB投入【商用復旧】　→　⑧各棟の負荷復旧・VWC投入・機能確認（部隊立会）・完了報告</t>
         </is>
       </c>
       <c r="D15" s="10" t="n"/>
@@ -14249,7 +14323,7 @@
       </c>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>仮設給電なし。約57時間（12/23 9:00頃～12/25 17:30頃）停止。「6.4」による</t>
+          <t>仮設給電なし。約56時間（12/23 9:00頃～12/25 16:45頃）停止。「6.4」による</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14382,7 @@
       </c>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>約57時間（12/23 9:00頃～12/25 17:30頃）停電</t>
+          <t>約56時間（12/23 9:00頃～12/25 16:45頃）停電</t>
         </is>
       </c>
     </row>
@@ -14367,14 +14441,14 @@
       </c>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>約57時間（12/23 9:00頃～12/25 17:30頃）停電。影響を部隊と確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="29.9" customHeight="1">
+          <t>約56時間（12/23 9:00頃～12/25 16:45頃）停電。影響を部隊と確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45.5" customHeight="1">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>※　仮設給電を行う負荷の停電は、12/23 9:00頃～11:45頃（仮設切替）及び12/25 15:40頃～17:30頃（商用復旧）の切替時に限る予定。</t>
+          <t>※　仮設給電を行う負荷の停電は、12/23 9:00頃～11:45頃（仮設切替）及び12/25 14:15頃～16:45頃（商用復旧）の切替時に限る予定（12/25は受電所14:15頃・整備格納庫15:00頃・補給倉庫棟15:35頃から停電）。</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14525,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="26" t="inlineStr">
         <is>
-          <t>仮設給電を行わない建物（厚生棟・倉庫棟等）が約57時間（12/23 9:00頃～12/25 17:30頃）停電することの影響（冷凍冷蔵・給排水・通信・警備・暖房等）と事前措置</t>
+          <t>仮設給電を行わない建物（厚生棟・倉庫棟等）が約56時間（12/23 9:00頃～12/25 16:45頃）停電することの影響（冷凍冷蔵・給排水・通信・警備・暖房等）と事前措置</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -14556,7 +14630,7 @@
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t>仮設切替時（12/23 9:00～11:45頃）及び商用復旧時（12/25 15:40～17:30頃）の停電に対する措置（事前停止・UPS保持・切替時刻の調整等）</t>
+          <t>仮設切替時（12/23 9:00～11:45頃）及び商用復旧時（12/25 14:15～16:45頃）の停電に対する措置（事前停止・UPS保持・切替時刻の調整等）</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -15139,7 +15213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -17356,7 +17430,7 @@
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>9:00　～　17:45頃　（作業前ミーティング8:30～/試験・検査終了後に復電、商用切替・負荷確認を含め17:45頃終了予定）</t>
+          <t>9:00　～　17:00頃　（作業前ミーティング8:30～/試験・検査終了後に復電、商用切替・負荷確認を含め17:00頃終了予定）</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
@@ -17821,7 +17895,7 @@
       </c>
       <c r="I77" s="32" t="n"/>
     </row>
-    <row r="78" ht="28.6" customHeight="1">
+    <row r="78" ht="88.5" customHeight="1">
       <c r="A78" s="32" t="inlineStr">
         <is>
           <t>10</t>
@@ -17834,211 +17908,211 @@
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>㈱アート
+㈱別川製作所</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>受電所：発電機停止・仮設ケーブル切離し、低圧母線絶縁抵抗測定、2次導体母線側接続（⑥⑦⑧⑨⑭）</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="inlineStr">
+        <is>
+          <t>高圧停電・作業用接地中に実施【受電所 低圧停電】。締付トルク記録。試験・検査の前に接続を完了し、接続部を検査対象に含める。以降、電気室は投光器（バッテリー式等）で照明</t>
+        </is>
+      </c>
+      <c r="H78" s="32" t="inlineStr">
+        <is>
+          <t>中村</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="n"/>
+    </row>
+    <row r="79" ht="28.6" customHeight="1">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E78" s="33" t="inlineStr">
+      <c r="E79" s="33" t="inlineStr">
         <is>
           <t>試験準備・盤内最終確認</t>
         </is>
       </c>
-      <c r="F78" s="32" t="inlineStr">
+      <c r="F79" s="32" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G78" s="33" t="inlineStr">
+      <c r="G79" s="33" t="inlineStr">
         <is>
           <t>試験区画の設定、工具・材料の残置確認（指差呼称）</t>
         </is>
       </c>
-      <c r="H78" s="32" t="inlineStr">
+      <c r="H79" s="32" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I78" s="32" t="n"/>
-    </row>
-    <row r="79" ht="65.90000000000001" customHeight="1">
-      <c r="A79" s="32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="I79" s="32" t="n"/>
+    </row>
+    <row r="80" ht="28.6" customHeight="1">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>作 業 班</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>作業・業務項目</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>停電</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>補足事項・確認内容</t>
+        </is>
+      </c>
+      <c r="H80" s="31" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
+      <c r="I80" s="31" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="88.5" customHeight="1">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>関西電気保安協会
 ㈱アート</t>
         </is>
       </c>
-      <c r="E79" s="33" t="inlineStr">
-        <is>
-          <t>試験・検査（絶縁抵抗・絶縁耐力・保護継電器（OCR・UVR・地絡）・受電前検査）</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
+      <c r="E81" s="33" t="inlineStr">
+        <is>
+          <t>試験・検査（復電前の絶縁抵抗（2次導体接続部を含む）・絶縁耐力・保護継電器（OCR・UVR・地絡）・受電前検査）</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G79" s="33" t="inlineStr">
-        <is>
-          <t>所要時間・試験範囲は保安協会と協議（要確認）。作業用接地は電気主任技術者の指示で一時取外し・再取付（記録）。試験区画は立入禁止</t>
-        </is>
-      </c>
-      <c r="H79" s="32" t="inlineStr">
+      <c r="G81" s="33" t="inlineStr">
+        <is>
+          <t>所要時間・試験範囲は保安協会と協議（要確認）。作業用接地は電気主任技術者の指示で一時取外し・再取付（記録）。試験区画は立入禁止。試験用電源（小型発電機等）は要確認</t>
+        </is>
+      </c>
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I79" s="32" t="n"/>
-    </row>
-    <row r="80" ht="28.6" customHeight="1">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B80" s="31" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>作 業 班</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>作業・業務項目</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>停電</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>補足事項・確認内容</t>
-        </is>
-      </c>
-      <c r="H80" s="31" t="inlineStr">
-        <is>
-          <t>責任者</t>
-        </is>
-      </c>
-      <c r="I80" s="31" t="inlineStr">
-        <is>
-          <t>進捗</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="43.3" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="I81" s="32" t="n"/>
+    </row>
+    <row r="82" ht="43.3" customHeight="1">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
         <is>
           <t>㈱アート
 ㈱関西テクノ</t>
         </is>
       </c>
-      <c r="E81" s="33" t="inlineStr">
+      <c r="E82" s="33" t="inlineStr">
         <is>
           <t>整備格納庫：発電機停止・仮設ケーブル切離し、逆送防止措置の復旧</t>
         </is>
       </c>
-      <c r="F81" s="32" t="inlineStr">
+      <c r="F82" s="32" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="G81" s="33" t="inlineStr">
+      <c r="G82" s="33" t="inlineStr">
         <is>
           <t>【低圧停電】。復旧完了・退避を作業指揮者へ無線で報告（写真記録）</t>
         </is>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H82" s="32" t="inlineStr">
         <is>
           <t>切替班長</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="n"/>
-    </row>
-    <row r="82" ht="54.6" customHeight="1">
-      <c r="A82" s="32" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>㈱アート
-㈱別川製作所</t>
-        </is>
-      </c>
-      <c r="E82" s="33" t="inlineStr">
-        <is>
-          <t>受電所：発電機停止・仮設ケーブル切離し、低圧母線絶縁抵抗測定、2次導体母線側接続（⑥⑦⑧⑨⑭）</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G82" s="33" t="inlineStr">
-        <is>
-          <t>高圧停電・作業用接地中に実施【低圧停電】。締付トルク記録</t>
-        </is>
-      </c>
-      <c r="H82" s="32" t="inlineStr">
-        <is>
-          <t>中村</t>
         </is>
       </c>
       <c r="I82" s="32" t="n"/>
@@ -18051,12 +18125,12 @@
       </c>
       <c r="B83" s="32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D83" s="32" t="inlineStr">
@@ -18087,7 +18161,7 @@
       </c>
       <c r="I83" s="32" t="n"/>
     </row>
-    <row r="84" ht="28.6" customHeight="1">
+    <row r="84" ht="43.3" customHeight="1">
       <c r="A84" s="32" t="inlineStr">
         <is>
           <t>15</t>
@@ -18095,22 +18169,22 @@
       </c>
       <c r="B84" s="32" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D84" s="32" t="inlineStr">
         <is>
-          <t>㈱アート</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="E84" s="33" t="inlineStr">
         <is>
-          <t>復電前絶縁抵抗測定（2次導体接続部を含む）</t>
+          <t>受電所作業者の集合・別棟の完了報告受領、作業用接地取外し・最終確認</t>
         </is>
       </c>
       <c r="F84" s="32" t="inlineStr">
@@ -18120,17 +18194,17 @@
       </c>
       <c r="G84" s="33" t="inlineStr">
         <is>
-          <t>規定値以上を確認し記録</t>
+          <t>取外し数量（9組）の照合。整備格納庫・補給倉庫棟の作業完了・退避報告を確認</t>
         </is>
       </c>
       <c r="H84" s="32" t="inlineStr">
         <is>
-          <t>中村</t>
+          <t>足立/中村</t>
         </is>
       </c>
       <c r="I84" s="32" t="n"/>
     </row>
-    <row r="85" ht="43.3" customHeight="1">
+    <row r="85" ht="28.6" customHeight="1">
       <c r="A85" s="32" t="inlineStr">
         <is>
           <t>16</t>
@@ -18138,22 +18212,22 @@
       </c>
       <c r="B85" s="32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="D85" s="32" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>電気主任技術者</t>
         </is>
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t>受電所作業者の集合・別棟の完了報告受領、作業用接地取外し・最終確認</t>
+          <t>3PDS投入（無電圧）</t>
         </is>
       </c>
       <c r="F85" s="32" t="inlineStr">
@@ -18163,17 +18237,17 @@
       </c>
       <c r="G85" s="33" t="inlineStr">
         <is>
-          <t>取外し数量の照合。整備格納庫・補給倉庫棟の作業完了・退避報告を確認</t>
+          <t>全VCB・LBS・VWCの開放を確認。操作禁止札撤去</t>
         </is>
       </c>
       <c r="H85" s="32" t="inlineStr">
         <is>
-          <t>足立/中村</t>
+          <t>足立</t>
         </is>
       </c>
       <c r="I85" s="32" t="n"/>
     </row>
-    <row r="86" ht="28.6" customHeight="1">
+    <row r="86" ht="54.6" customHeight="1">
       <c r="A86" s="32" t="inlineStr">
         <is>
           <t>17</t>
@@ -18181,72 +18255,68 @@
       </c>
       <c r="B86" s="32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D86" s="32" t="inlineStr">
-        <is>
-          <t>電気主任技術者</t>
-        </is>
-      </c>
-      <c r="E86" s="33" t="inlineStr">
-        <is>
-          <t>3PDS投入（無電圧）</t>
-        </is>
-      </c>
-      <c r="F86" s="32" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="G86" s="33" t="inlineStr">
-        <is>
-          <t>全VCB・LBS・VWCの開放を確認。操作禁止札撤去</t>
-        </is>
-      </c>
-      <c r="H86" s="32" t="inlineStr">
-        <is>
-          <t>足立</t>
-        </is>
-      </c>
-      <c r="I86" s="32" t="n"/>
-    </row>
-    <row r="87" ht="54.6" customHeight="1">
-      <c r="A87" s="32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B87" s="32" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="C87" s="32" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>電気主任技術者
 PAS操作補助員</t>
         </is>
       </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>引込柱PAS投入　【高圧受電】</t>
+        </is>
+      </c>
+      <c r="F86" s="32" t="n"/>
+      <c r="G86" s="33" t="inlineStr">
+        <is>
+          <t>施錠・操作禁止札撤去。受電所側と無線で相互確認</t>
+        </is>
+      </c>
+      <c r="H86" s="32" t="inlineStr">
+        <is>
+          <t>足立</t>
+        </is>
+      </c>
+      <c r="I86" s="32" t="n"/>
+    </row>
+    <row r="87" ht="65.90000000000001" customHeight="1">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="D87" s="32" t="inlineStr">
+        <is>
+          <t>電気主任技術者</t>
+        </is>
+      </c>
       <c r="E87" s="33" t="inlineStr">
         <is>
-          <t>引込柱PAS投入　【高圧受電】</t>
+          <t>受電VCB投入、電圧・相回転確認、母線連絡VCB・LBS（89-1・89-2・89-3・89-5）順次投入　【受電所 商用復旧】</t>
         </is>
       </c>
       <c r="F87" s="32" t="n"/>
       <c r="G87" s="33" t="inlineStr">
         <is>
-          <t>施錠・操作禁止札撤去。受電所側と無線で相互確認</t>
+          <t>変圧器の異音・励磁状態を確認。盤扉閉・充電部への接近禁止</t>
         </is>
       </c>
       <c r="H87" s="32" t="inlineStr">
@@ -18256,7 +18326,7 @@
       </c>
       <c r="I87" s="32" t="n"/>
     </row>
-    <row r="88" ht="65.90000000000001" customHeight="1">
+    <row r="88" ht="43.3" customHeight="1">
       <c r="A88" s="32" t="inlineStr">
         <is>
           <t>19</t>
@@ -18264,12 +18334,12 @@
       </c>
       <c r="B88" s="32" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="D88" s="32" t="inlineStr">
@@ -18279,13 +18349,13 @@
       </c>
       <c r="E88" s="33" t="inlineStr">
         <is>
-          <t>受電VCB投入、電圧・相回転確認、母線連絡VCB・LBS（89-1・89-2・89-3・89-5）順次投入　【受電所 商用復旧】</t>
+          <t>饋電VCB（F1・F5、F2・F6、F3・F7）投入　【各棟へ送電】</t>
         </is>
       </c>
       <c r="F88" s="32" t="n"/>
       <c r="G88" s="33" t="inlineStr">
         <is>
-          <t>変圧器の異音・励磁状態を確認。盤扉閉・充電部への接近禁止</t>
+          <t>整備格納庫・補給倉庫棟の復旧完了報告を確認のうえ投入</t>
         </is>
       </c>
       <c r="H88" s="32" t="inlineStr">
@@ -18295,7 +18365,7 @@
       </c>
       <c r="I88" s="32" t="n"/>
     </row>
-    <row r="89" ht="43.3" customHeight="1">
+    <row r="89" ht="54.6" customHeight="1">
       <c r="A89" s="32" t="inlineStr">
         <is>
           <t>20</t>
@@ -18303,98 +18373,78 @@
       </c>
       <c r="B89" s="32" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D89" s="32" t="inlineStr">
         <is>
-          <t>電気主任技術者</t>
+          <t>全員
+電気主任技術者</t>
         </is>
       </c>
       <c r="E89" s="33" t="inlineStr">
         <is>
-          <t>饋電VCB（F1・F5、F2・F6、F3・F7）投入　【各棟へ送電】</t>
+          <t>各棟の負荷復旧・機能確認、VWC（APFC）投入、既設発電設備等の復帰、最終確認・完了報告</t>
         </is>
       </c>
       <c r="F89" s="32" t="n"/>
       <c r="G89" s="33" t="inlineStr">
         <is>
-          <t>整備格納庫・補給倉庫棟の復旧完了報告を確認のうえ投入</t>
+          <t>消火ポンプユニット・排煙機・管制負荷の運転可能状態を含め、部隊立会のもと確認</t>
         </is>
       </c>
       <c r="H89" s="32" t="inlineStr">
         <is>
-          <t>足立</t>
+          <t>中村</t>
         </is>
       </c>
       <c r="I89" s="32" t="n"/>
     </row>
-    <row r="90" ht="54.6" customHeight="1">
-      <c r="A90" s="32" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B90" s="32" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C90" s="32" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="D90" s="32" t="inlineStr">
-        <is>
-          <t>全員
-電気主任技術者</t>
-        </is>
-      </c>
-      <c r="E90" s="33" t="inlineStr">
-        <is>
-          <t>各棟の負荷復旧・機能確認、VWC（APFC）投入、既設発電設備等の復帰、最終確認・完了報告</t>
-        </is>
-      </c>
-      <c r="F90" s="32" t="n"/>
-      <c r="G90" s="33" t="inlineStr">
-        <is>
-          <t>消火ポンプユニット・排煙機・管制負荷の運転可能状態を含め、部隊立会のもと確認</t>
-        </is>
-      </c>
-      <c r="H90" s="32" t="inlineStr">
-        <is>
-          <t>中村</t>
-        </is>
-      </c>
-      <c r="I90" s="32" t="n"/>
-    </row>
-    <row r="91" ht="5" customHeight="1">
-      <c r="A91" s="1" t="n"/>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="28" t="inlineStr">
+    <row r="90" ht="5" customHeight="1">
+      <c r="A90" s="1" t="n"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>7.5　令和8年12月26日（土）　仮設撤去工事</t>
         </is>
       </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>工 事 内 容</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>仮設発電機・仮設配管配線の撤去及び原状復旧（3か所・停電なし）</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="8" t="n"/>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="30" t="inlineStr">
         <is>
-          <t>工 事 内 容</t>
+          <t>作業予定時間</t>
         </is>
       </c>
       <c r="B93" s="10" t="n"/>
       <c r="C93" s="8" t="n"/>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>仮設発電機・仮設配管配線の撤去及び原状復旧（3か所・停電なし）</t>
+          <t>9:00　～　16:00　（作業前ミーティング　8:45～）</t>
         </is>
       </c>
       <c r="E93" s="10" t="n"/>
@@ -18406,14 +18456,14 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="30" t="inlineStr">
         <is>
-          <t>作業予定時間</t>
+          <t>作 業 員</t>
         </is>
       </c>
       <c r="B94" s="10" t="n"/>
       <c r="C94" s="8" t="n"/>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>9:00　～　16:00　（作業前ミーティング　8:45～）</t>
+          <t>㈱アート6名（作業指揮者を含む）</t>
         </is>
       </c>
       <c r="E94" s="10" t="n"/>
@@ -18422,102 +18472,122 @@
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="8" t="n"/>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="30" t="inlineStr">
-        <is>
-          <t>作 業 員</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="23" t="inlineStr">
-        <is>
-          <t>㈱アート6名（作業指揮者を含む）</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="n"/>
-      <c r="F95" s="10" t="n"/>
-      <c r="G95" s="10" t="n"/>
-      <c r="H95" s="10" t="n"/>
-      <c r="I95" s="8" t="n"/>
+    <row r="95" ht="28.6" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="inlineStr">
+        <is>
+          <t>作 業 班</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>作業・業務項目</t>
+        </is>
+      </c>
+      <c r="F95" s="31" t="inlineStr">
+        <is>
+          <t>停電</t>
+        </is>
+      </c>
+      <c r="G95" s="31" t="inlineStr">
+        <is>
+          <t>補足事項・確認内容</t>
+        </is>
+      </c>
+      <c r="H95" s="31" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
+      <c r="I95" s="31" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="28.6" customHeight="1">
-      <c r="A96" s="31" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B96" s="31" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="C96" s="31" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="D96" s="31" t="inlineStr">
-        <is>
-          <t>作 業 班</t>
-        </is>
-      </c>
-      <c r="E96" s="31" t="inlineStr">
-        <is>
-          <t>作業・業務項目</t>
-        </is>
-      </c>
-      <c r="F96" s="31" t="inlineStr">
-        <is>
-          <t>停電</t>
-        </is>
-      </c>
-      <c r="G96" s="31" t="inlineStr">
-        <is>
-          <t>補足事項・確認内容</t>
-        </is>
-      </c>
-      <c r="H96" s="31" t="inlineStr">
-        <is>
-          <t>責任者</t>
-        </is>
-      </c>
-      <c r="I96" s="31" t="inlineStr">
-        <is>
-          <t>進捗</t>
-        </is>
-      </c>
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="E96" s="33" t="inlineStr">
+        <is>
+          <t>作業前ミーティング・KY活動、保護具・工具点検</t>
+        </is>
+      </c>
+      <c r="F96" s="32" t="n"/>
+      <c r="G96" s="33" t="inlineStr">
+        <is>
+          <t>撤去手順・作業区画の確認</t>
+        </is>
+      </c>
+      <c r="H96" s="32" t="inlineStr">
+        <is>
+          <t>中村</t>
+        </is>
+      </c>
+      <c r="I96" s="32" t="n"/>
     </row>
     <row r="97" ht="28.6" customHeight="1">
       <c r="A97" s="32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" s="32" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="D97" s="32" t="inlineStr">
         <is>
-          <t>全員</t>
+          <t>㈱アート</t>
         </is>
       </c>
       <c r="E97" s="33" t="inlineStr">
         <is>
-          <t>作業前ミーティング・KY活動、保護具・工具点検</t>
+          <t>区画設置、仮設ケーブル盤側端末の撤去確認</t>
         </is>
       </c>
       <c r="F97" s="32" t="n"/>
       <c r="G97" s="33" t="inlineStr">
         <is>
-          <t>撤去手順・作業区画の確認</t>
+          <t>盤側は12/25に切離し済み。盤内の絶縁・残置物を確認</t>
         </is>
       </c>
       <c r="H97" s="32" t="inlineStr">
@@ -18530,17 +18600,17 @@
     <row r="98" ht="28.6" customHeight="1">
       <c r="A98" s="32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B98" s="32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="D98" s="32" t="inlineStr">
@@ -18550,13 +18620,13 @@
       </c>
       <c r="E98" s="33" t="inlineStr">
         <is>
-          <t>区画設置、仮設ケーブル盤側端末の撤去確認</t>
+          <t>CET150sq（計24条）・FEP100　撤去</t>
         </is>
       </c>
       <c r="F98" s="32" t="n"/>
       <c r="G98" s="33" t="inlineStr">
         <is>
-          <t>盤側は12/25に切離し済み。盤内の絶縁・残置物を確認</t>
+          <t>撤去品の分別・整理</t>
         </is>
       </c>
       <c r="H98" s="32" t="inlineStr">
@@ -18569,17 +18639,17 @@
     <row r="99" ht="28.6" customHeight="1">
       <c r="A99" s="32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B99" s="32" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D99" s="32" t="inlineStr">
@@ -18589,15 +18659,11 @@
       </c>
       <c r="E99" s="33" t="inlineStr">
         <is>
-          <t>CET150sq（計24条）・FEP100　撤去</t>
+          <t>仮設接地撤去</t>
         </is>
       </c>
       <c r="F99" s="32" t="n"/>
-      <c r="G99" s="33" t="inlineStr">
-        <is>
-          <t>撤去品の分別・整理</t>
-        </is>
-      </c>
+      <c r="G99" s="33" t="n"/>
       <c r="H99" s="32" t="inlineStr">
         <is>
           <t>中村</t>
@@ -18608,130 +18674,134 @@
     <row r="100" ht="28.6" customHeight="1">
       <c r="A100" s="32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B100" s="32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D100" s="32" t="inlineStr">
         <is>
-          <t>㈱アート</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E100" s="33" t="inlineStr">
         <is>
-          <t>仮設接地撤去</t>
+          <t>昼休憩</t>
         </is>
       </c>
       <c r="F100" s="32" t="n"/>
       <c r="G100" s="33" t="n"/>
-      <c r="H100" s="32" t="inlineStr">
+      <c r="H100" s="32" t="n"/>
+      <c r="I100" s="32" t="n"/>
+    </row>
+    <row r="101" ht="28.6" customHeight="1">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>開始</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>終了</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="inlineStr">
+        <is>
+          <t>作 業 班</t>
+        </is>
+      </c>
+      <c r="E101" s="31" t="inlineStr">
+        <is>
+          <t>作業・業務項目</t>
+        </is>
+      </c>
+      <c r="F101" s="31" t="inlineStr">
+        <is>
+          <t>停電</t>
+        </is>
+      </c>
+      <c r="G101" s="31" t="inlineStr">
+        <is>
+          <t>補足事項・確認内容</t>
+        </is>
+      </c>
+      <c r="H101" s="31" t="inlineStr">
+        <is>
+          <t>責任者</t>
+        </is>
+      </c>
+      <c r="I101" s="31" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28.6" customHeight="1">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="inlineStr">
+        <is>
+          <t>㈱アート</t>
+        </is>
+      </c>
+      <c r="E102" s="33" t="inlineStr">
+        <is>
+          <t>仮設発電機8台　搬出</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="n"/>
+      <c r="G102" s="33" t="inlineStr">
+        <is>
+          <t>燃料残量・油漏れの確認</t>
+        </is>
+      </c>
+      <c r="H102" s="32" t="inlineStr">
         <is>
           <t>中村</t>
         </is>
       </c>
-      <c r="I100" s="32" t="n"/>
-    </row>
-    <row r="101" ht="28.6" customHeight="1">
-      <c r="A101" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B101" s="32" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C101" s="32" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D101" s="32" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E101" s="33" t="inlineStr">
-        <is>
-          <t>昼休憩</t>
-        </is>
-      </c>
-      <c r="F101" s="32" t="n"/>
-      <c r="G101" s="33" t="n"/>
-      <c r="H101" s="32" t="n"/>
-      <c r="I101" s="32" t="n"/>
-    </row>
-    <row r="102" ht="28.6" customHeight="1">
-      <c r="A102" s="31" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B102" s="31" t="inlineStr">
-        <is>
-          <t>開始</t>
-        </is>
-      </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>終了</t>
-        </is>
-      </c>
-      <c r="D102" s="31" t="inlineStr">
-        <is>
-          <t>作 業 班</t>
-        </is>
-      </c>
-      <c r="E102" s="31" t="inlineStr">
-        <is>
-          <t>作業・業務項目</t>
-        </is>
-      </c>
-      <c r="F102" s="31" t="inlineStr">
-        <is>
-          <t>停電</t>
-        </is>
-      </c>
-      <c r="G102" s="31" t="inlineStr">
-        <is>
-          <t>補足事項・確認内容</t>
-        </is>
-      </c>
-      <c r="H102" s="31" t="inlineStr">
-        <is>
-          <t>責任者</t>
-        </is>
-      </c>
-      <c r="I102" s="31" t="inlineStr">
-        <is>
-          <t>進捗</t>
-        </is>
-      </c>
+      <c r="I102" s="32" t="n"/>
     </row>
     <row r="103" ht="28.6" customHeight="1">
       <c r="A103" s="32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B103" s="32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D103" s="32" t="inlineStr">
@@ -18741,13 +18811,13 @@
       </c>
       <c r="E103" s="33" t="inlineStr">
         <is>
-          <t>仮設発電機8台　搬出</t>
+          <t>原状復旧・清掃、オイルパン・吸着マット撤去</t>
         </is>
       </c>
       <c r="F103" s="32" t="n"/>
       <c r="G103" s="33" t="inlineStr">
         <is>
-          <t>燃料残量・油漏れの確認</t>
+          <t>設置場所の損傷・油染みの有無を確認</t>
         </is>
       </c>
       <c r="H103" s="32" t="inlineStr">
@@ -18760,33 +18830,33 @@
     <row r="104" ht="28.6" customHeight="1">
       <c r="A104" s="32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B104" s="32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D104" s="32" t="inlineStr">
         <is>
-          <t>㈱アート</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="E104" s="33" t="inlineStr">
         <is>
-          <t>原状復旧・清掃、オイルパン・吸着マット撤去</t>
+          <t>新設変圧器の運転状態確認・完了報告</t>
         </is>
       </c>
       <c r="F104" s="32" t="n"/>
       <c r="G104" s="33" t="inlineStr">
         <is>
-          <t>設置場所の損傷・油染みの有無を確認</t>
+          <t>温度・異音・電圧を確認し記録。監督官・部隊へ報告</t>
         </is>
       </c>
       <c r="H104" s="32" t="inlineStr">
@@ -18796,52 +18866,13 @@
       </c>
       <c r="I104" s="32" t="n"/>
     </row>
-    <row r="105" ht="28.6" customHeight="1">
-      <c r="A105" s="32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B105" s="32" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="C105" s="32" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="D105" s="32" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="E105" s="33" t="inlineStr">
-        <is>
-          <t>新設変圧器の運転状態確認・完了報告</t>
-        </is>
-      </c>
-      <c r="F105" s="32" t="n"/>
-      <c r="G105" s="33" t="inlineStr">
-        <is>
-          <t>温度・異音・電圧を確認し記録。監督官・部隊へ報告</t>
-        </is>
-      </c>
-      <c r="H105" s="32" t="inlineStr">
-        <is>
-          <t>中村</t>
-        </is>
-      </c>
-      <c r="I105" s="32" t="n"/>
-    </row>
-    <row r="106" ht="5" customHeight="1">
-      <c r="A106" s="1" t="n"/>
+    <row r="105" ht="5" customHeight="1">
+      <c r="A105" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="D49:I49"/>
-    <mergeCell ref="D95:I95"/>
+    <mergeCell ref="A90:I90"/>
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A18:I18"/>
@@ -18849,7 +18880,7 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D48:I48"/>
     <mergeCell ref="D66:I66"/>
-    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A105:I105"/>
     <mergeCell ref="D47:I47"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A47:C47"/>
@@ -18857,9 +18888,9 @@
     <mergeCell ref="D93:I93"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A106:I106"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D92:I92"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A63:I63"/>
@@ -18868,9 +18899,9 @@
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D94:I94"/>
     <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A92:C92"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A92:I92"/>
     <mergeCell ref="A64:I64"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A94:C94"/>
@@ -18899,7 +18930,7 @@
     <brk id="35" min="0" max="16383" man="1"/>
     <brk id="58" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="101" min="0" max="16383" man="1"/>
+    <brk id="100" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
